--- a/comparison_table.xlsx
+++ b/comparison_table.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="training_details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,51 +417,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Tracker</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Backbone</t>
+          <t>HOTA ↑</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Params (M) ↓</t>
+          <t>MOTA ↑</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>FLOPs (G) ↓</t>
+          <t>IDF1 ↑</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>P ↑</t>
+          <t>AssA ↑</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>R ↑</t>
+          <t>DetA ↑</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>mAP@0.5 ↑</t>
+          <t>IDSW ↓</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>mAP@0.5:0.95 ↑</t>
+          <t>FP ↓</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>FN ↓</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>FPS ↑</t>
         </is>
@@ -471,415 +475,313 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Faster R-CNN</t>
+          <t>ByteTrack</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ResNet-50-FPN</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>41.30</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.8724</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.9888</t>
+          <t>0.9 †</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.9864</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4012 †</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>492.9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSD300</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VGG-16</t>
+          <t>OC-SORT</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>0.9865</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.9644</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.9791</t>
+          <t>187 †</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6861</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>39.6</t>
+          <t>7628</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>567.8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YOLOv5s</t>
+          <t>Deep OC-SORT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CSPDarknet53</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>9.12</t>
+          <t>0.8 †</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24.0 †</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.9818</t>
+          <t>0.8 †</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.9908</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.9893 †</t>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7997</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.7 †</t>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YOLOv8s</t>
+          <t>StrongSORT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C2f-Darknet</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11.14</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9823</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.9919 †</t>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>0.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.9893</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.7985</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>87.4</t>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>30607</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>YOLOv11s</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BoT-SORT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C3k2-Darknet</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>9.43 †</t>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.9853 †</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.9903</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>0.9894</t>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.8057 †</t>
+          <t>9136 †</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19.7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RT-DETR-L</t>
+          <t>HybridSORT †</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HGNetv2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>0.9 †</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>109.9</t>
+          <t>0.8 †</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.9606</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>0.9934</t>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.9887</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>0.8114</t>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7727</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.9</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Epochs</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Training time (min)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Input size</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Faster R-CNN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SSD300</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>YOLOv5s</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D4" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>YOLOv8s</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D5" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>YOLOv11s</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RT-DETR-L</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C7" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>640</v>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
       </c>
     </row>
   </sheetData>
